--- a/data/avito_photos.xlsx
+++ b/data/avito_photos.xlsx
@@ -436,7 +436,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/01X301127C_1.jpg?v=80a1acf4b1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/01X301127C_2.jpg?v=3bc5b750c8</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/01X301127C_1.jpg?v=3bc5b750c8</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_2.jpg?v=44a9ab31fd</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_1.jpg?v=c45a2498aa|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_2.jpg?v=44a9ab31fd</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769D_1.jpg?v=ea79e81563|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769D_2.jpg?v=4529f855b6</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769D_2.jpg?v=4529f855b6</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/klipsy-shtokov-2sht_1.jpg?v=9eba78df5d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/klipsy-shtokov-2sht_2.jpg?v=5cb33fddae</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/klipsy-shtokov-2sht_2.jpg?v=5cb33fddae</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/nakladki-pedali_1.jpg?v=20a8430969|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/nakladki-pedali_2.jpg?v=c459949afe</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/nakladki-pedali_1.jpg?v=c459949afe|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/nakladki-pedali_2.jpg?v=20a8430969</t>
         </is>
       </c>
     </row>

--- a/data/avito_photos.xlsx
+++ b/data/avito_photos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B68"/>
+  <dimension ref="A1:B73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -803,430 +803,490 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0cw0am</t>
+          <t>0am325477</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_1.jpg?v=d9a6257d65|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_2.jpg?v=2e5ae40f99|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_3.jpg?v=452fb81089</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477_1.jpg?v=76f197e896</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0cw0am325025</t>
+          <t>0cw0am</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025_1.jpg?v=98f28523c2</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_1.jpg?v=d9a6257d65|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_2.jpg?v=2e5ae40f99|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_3.jpg?v=452fb81089</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0cw0amdsgdq200</t>
+          <t>0cw0am325025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0amdsgdq200_1.jpg?v=77a111eb34|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0amdsgdq200_2.jpg?v=40c2597cb3</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025_1.jpg?v=98f28523c2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0cw325025h</t>
+          <t>0cw0amdsgdq200</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_1.jpg?v=0c3047157b|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_2.jpg?v=209a640347</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0amdsgdq200_1.jpg?v=77a111eb34|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0amdsgdq200_2.jpg?v=40c2597cb3</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0сц</t>
+          <t>0cw325025h</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._1.jpg?v=3e0abf9ec7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._2.jpg?v=b12c6dac21|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._3.jpg?v=bd237a81d2</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_1.jpg?v=0c3047157b|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_2.jpg?v=209a640347</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>317053TX0C</t>
+          <t>0сц</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_1.jpg?v=ff760a00af|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_2.jpg?v=8cf63c6906</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._1.jpg?v=3e0abf9ec7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._2.jpg?v=b12c6dac21|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._3.jpg?v=bd237a81d2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>55565480</t>
+          <t>317053TX0C</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/55565480_1.jpg?v=0ff6bde457</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_1.jpg?v=ff760a00af|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_2.jpg?v=8cf63c6906</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>6t30</t>
+          <t>55565480</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/6t30_1.jpg?v=eb7c8272e8</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/55565480_1.jpg?v=0ff6bde457</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Dq200dsg70am0cw</t>
+          <t>6t30</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq200dsg70am0cw_1.jpg?v=0087449119</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/6t30_1.jpg?v=eb7c8272e8</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Dq500</t>
+          <t>Dq200dsg70am0cw</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_1.jpg?v=b2dce2c6a2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_10.jpg?v=4782f6a203|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_11.jpg?v=b00b729a6f|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_12.jpg?v=3e5bb95f61|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_13.jpg?v=b5e4690bb8|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_14.jpg?v=293affdbb4|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_2.jpg?v=01450abeda|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_3.jpg?v=8b53715593|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_4.jpg?v=87672fa5cf|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_5.jpg?v=22b635f676|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_6.jpg?v=60c3947305|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_7.jpg?v=6455c2a999|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_8.jpg?v=1c56d278b5|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_9.jpg?v=0e28b9ca1b</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq200dsg70am0cw_1.jpg?v=0087449119</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>EA888</t>
+          <t>Dq500</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/EA888_1.jpg?v=334ca088dc|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/EA888_2.jpg?v=dfb4c007bb|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/EA888_3.jpg?v=a0f5f5592e</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_1.jpg?v=b2dce2c6a2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_10.jpg?v=4782f6a203|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_11.jpg?v=b00b729a6f|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_12.jpg?v=3e5bb95f61|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_13.jpg?v=b5e4690bb8|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_14.jpg?v=293affdbb4|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_2.jpg?v=01450abeda|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_3.jpg?v=8b53715593|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_4.jpg?v=87672fa5cf|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_5.jpg?v=22b635f676|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_6.jpg?v=60c3947305|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_7.jpg?v=6455c2a999|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_8.jpg?v=1c56d278b5|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_9.jpg?v=0e28b9ca1b</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>WHT001922</t>
+          <t>EA888</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/WHT001922_1.jpg?v=bb075186cb</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/EA888_1.jpg?v=334ca088dc|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/EA888_2.jpg?v=dfb4c007bb|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/EA888_3.jpg?v=a0f5f5592e</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>filtr-setka-0b5-orig</t>
+          <t>WHT001922</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_1.jpg?v=be20ada597|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_2.jpg?v=87268821a3</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/WHT001922_1.jpg?v=bb075186cb</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>gidroakkumulyator-orig</t>
+          <t>filtr-dsg7-dq200</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_1.jpg?v=51769ba372|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_2.jpg?v=2344c05b66|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_3.jpg?v=39719028b1</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-dsg7-dq200_1.jpg?v=817beb8c10</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>jf011e</t>
+          <t>filtr-setka-0b5-orig</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/jf011e_1.jpg?v=e8e0f28d81|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/jf011e_2.jpg?v=fd3d1e7343</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_1.jpg?v=be20ada597|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_2.jpg?v=87268821a3</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>klipsy-shtokov-2sht</t>
+          <t>gidroakkumulyator-orig</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/klipsy-shtokov-2sht_2.jpg?v=5cb33fddae</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_1.jpg?v=51769ba372|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_2.jpg?v=2344c05b66|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_3.jpg?v=39719028b1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>nakladki-pedali</t>
+          <t>jf011e</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/nakladki-pedali_1.jpg?v=c459949afe|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/nakladki-pedali_2.jpg?v=20a8430969</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/jf011e_1.jpg?v=e8e0f28d81|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/jf011e_2.jpg?v=fd3d1e7343</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>planka-solenoid-2sht</t>
+          <t>klipsy-shtokov-2sht</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/planka-solenoid-2sht_1.jpg?v=9d40871c3a</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/klipsy-shtokov-2sht_2.jpg?v=5cb33fddae</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>plastiny-solenoid-orig</t>
+          <t>nakladki-pedali</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastiny-solenoid-orig_1.jpg?v=d1b347b9af|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastiny-solenoid-orig_2.jpg?v=abefbc6b13</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/nakladki-pedali_1.jpg?v=c459949afe|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/nakladki-pedali_2.jpg?v=20a8430969</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>plita-filtr</t>
+          <t>planka-solenoid-2sht</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_1.jpg?v=efa8557d9d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_2.jpg?v=759d463fe2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_3.jpg?v=3f11b4e476</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/planka-solenoid-2sht_1.jpg?v=9d40871c3a</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki</t>
+          <t>plastiny-solenoid-orig</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_1.jpg?v=de55e47d7c|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_2.jpg?v=f0ac7e97a2</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastiny-solenoid-orig_1.jpg?v=d1b347b9af|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastiny-solenoid-orig_2.jpg?v=abefbc6b13</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>podshipnik-vilki-6</t>
+          <t>plita-filtr</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_1.jpg?v=1755bb55b2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_2.jpg?v=db91a4455e</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_1.jpg?v=efa8557d9d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_2.jpg?v=759d463fe2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_3.jpg?v=3f11b4e476</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
+          <t>plita-filtr-orig</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki-v2_1.jpg?v=822e115d3a|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki-v2_2.jpg?v=67c916a623</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-orig_1.jpg?v=33c4d4baf2</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig-v2</t>
+          <t>plita-filtr-pylniki</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/remkomplekt-shtokov-orig-v2_1.jpg?v=f8bf2b9112</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_1.jpg?v=de55e47d7c|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_2.jpg?v=f0ac7e97a2</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig</t>
+          <t>plita-filtr-pylniki-sal-orig</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_1.jpg?v=e5a1740eeb|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_2.jpg?v=b6e630000c</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-sal-orig_1.jpg?v=663e730ff0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>salnik-tolkatelya-alum</t>
+          <t>plita-pylniki-salniki</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-tolkatelya-alum_1.jpg?v=b8838939fa</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki_1.jpg?v=03ce24da06</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>salniki-shtokov-2sht</t>
+          <t>podshipnik-vilki-6</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-2sht_1.jpg?v=aa8f5c5cf2</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_1.jpg?v=1755bb55b2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_2.jpg?v=db91a4455e</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>salniki-shtokov-orig</t>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-orig_1.jpg?v=4c8e4d8db5</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki-v2_1.jpg?v=822e115d3a|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki-v2_2.jpg?v=67c916a623</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>salniki-tolkatelya-4sht</t>
+          <t>remkomplekt-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_1.jpg?v=28323f6201|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_2.jpg?v=37b0cc95a1</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/remkomplekt-shtokov-orig-v2_1.jpg?v=f8bf2b9112</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>salnikprivod-l</t>
+          <t>salnik-shtoka-orig</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-l_1.jpg?v=2394757996</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_1.jpg?v=e5a1740eeb|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_2.jpg?v=b6e630000c</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>salnikprivod-r</t>
+          <t>salnik-tolkatelya-alum</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-r_1.jpg?v=c7ca0aca75</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-tolkatelya-alum_1.jpg?v=b8838939fa</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>salnikvhod</t>
+          <t>salniki-shtokov-2sht</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_1.jpg?v=fa7536c413|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_2.jpg?v=dc80d0c822</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-2sht_1.jpg?v=aa8f5c5cf2</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>stalnaya-vstavka-plity</t>
+          <t>salniki-shtokov-orig</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/stalnaya-vstavka-plity_1.jpg?v=b5aa54fe7d</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-orig_1.jpg?v=4c8e4d8db5</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>tolkateli-4-salniki-4</t>
+          <t>salniki-tolkatelya-4sht</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-4-salniki-4_1.jpg?v=6dd3ccd233</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_1.jpg?v=28323f6201|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_2.jpg?v=37b0cc95a1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>tolkateli-salniki-alum-komplekt</t>
+          <t>salnikprivod-l</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-salniki-alum-komplekt_1.jpg?v=c2f7c0583b</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-l_1.jpg?v=2394757996</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>salnikprivod-r</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-r_1.jpg?v=c7ca0aca75</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>salnikvhod</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_1.jpg?v=fa7536c413|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_2.jpg?v=dc80d0c822</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>stalnaya-vstavka-plity</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/stalnaya-vstavka-plity_1.jpg?v=b5aa54fe7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>tolkateli-4-salniki-4</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-4-salniki-4_1.jpg?v=6dd3ccd233</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>tolkateli-salniki-alum-komplekt</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-salniki-alum-komplekt_1.jpg?v=c2f7c0583b</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
           <t>vtulki-shtokov-2sht</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/vtulki-shtokov-2sht_1.jpg?v=c43f734ce2</t>
         </is>

--- a/data/avito_photos.xlsx
+++ b/data/avito_photos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B73"/>
+  <dimension ref="A1:B85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -616,7 +616,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_1.jpg?v=21cf6a4fc0</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_1.jpg?v=5bd8ad5ac3|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_2.jpg?v=21cf6a4fc0</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H_1.jpg?v=df6ff84458</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H_1.png?v=0593c687c2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H_2.jpg?v=df6ff84458</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025._1.jpg?v=3f30a503c8</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025._1.jpg?v=32a4eaa349|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025._2.jpg?v=3f30a503c8</t>
         </is>
       </c>
     </row>
@@ -815,478 +815,622 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0cw0am</t>
+          <t>0ambset</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_1.jpg?v=d9a6257d65|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_2.jpg?v=2e5ae40f99|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_3.jpg?v=452fb81089</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0ambset_1.jpg?v=ac2cbcb893|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0ambset_2.jpg?v=4021b295b7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0ambset_3.jpg?v=2c5f358ea8</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0cw0am325025</t>
+          <t>0cw0am</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025_1.jpg?v=98f28523c2</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_1.jpg?v=d9a6257d65|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_2.jpg?v=2e5ae40f99|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_3.jpg?v=452fb81089</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0cw0amdsgdq200</t>
+          <t>0cw0am325025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0amdsgdq200_1.jpg?v=77a111eb34|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0amdsgdq200_2.jpg?v=40c2597cb3</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025_1.jpg?v=98f28523c2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0cw325025h</t>
+          <t>0cw0amdsgdq200</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_1.jpg?v=0c3047157b|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_2.jpg?v=209a640347</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0amdsgdq200_1.jpg?v=d2723138aa|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0amdsgdq200_2.jpg?v=77a111eb34|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0amdsgdq200_3.jpg?v=40c2597cb3</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0сц</t>
+          <t>0cw325025h</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._1.jpg?v=3e0abf9ec7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._2.jpg?v=b12c6dac21|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._3.jpg?v=bd237a81d2</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_1.jpg?v=0c3047157b|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_2.jpg?v=209a640347</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>317053TX0C</t>
+          <t>0сц</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_1.jpg?v=ff760a00af|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_2.jpg?v=8cf63c6906</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._1.jpg?v=3e0abf9ec7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._2.jpg?v=b12c6dac21|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._3.jpg?v=bd237a81d2</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>55565480</t>
+          <t>317053TX0C</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/55565480_1.jpg?v=0ff6bde457</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_1.jpg?v=ff760a00af|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_2.jpg?v=8cf63c6906</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>6t30</t>
+          <t>55565480</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/6t30_1.jpg?v=eb7c8272e8</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/55565480_1.jpg?v=0ff6bde457</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Dq200dsg70am0cw</t>
+          <t>6t30</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq200dsg70am0cw_1.jpg?v=0087449119</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/6t30_1.jpg?v=eb7c8272e8</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Dq500</t>
+          <t>Dq200dsg70am0cw</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_1.jpg?v=b2dce2c6a2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_10.jpg?v=4782f6a203|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_11.jpg?v=b00b729a6f|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_12.jpg?v=3e5bb95f61|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_13.jpg?v=b5e4690bb8|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_14.jpg?v=293affdbb4|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_2.jpg?v=01450abeda|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_3.jpg?v=8b53715593|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_4.jpg?v=87672fa5cf|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_5.jpg?v=22b635f676|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_6.jpg?v=60c3947305|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_7.jpg?v=6455c2a999|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_8.jpg?v=1c56d278b5|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_9.jpg?v=0e28b9ca1b</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq200dsg70am0cw_1.jpg?v=0087449119</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>EA888</t>
+          <t>Dq500</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/EA888_1.jpg?v=334ca088dc|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/EA888_2.jpg?v=dfb4c007bb|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/EA888_3.jpg?v=a0f5f5592e</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_1.jpg?v=b2dce2c6a2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_10.jpg?v=4782f6a203|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_11.jpg?v=b00b729a6f|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_12.jpg?v=3e5bb95f61|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_13.jpg?v=b5e4690bb8|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_14.jpg?v=293affdbb4|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_2.jpg?v=01450abeda|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_3.jpg?v=8b53715593|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_4.jpg?v=87672fa5cf|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_5.jpg?v=22b635f676|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_6.jpg?v=60c3947305|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_7.jpg?v=6455c2a999|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_8.jpg?v=1c56d278b5|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_9.jpg?v=0e28b9ca1b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>WHT001922</t>
+          <t>EA888</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/WHT001922_1.jpg?v=bb075186cb</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/EA888_1.jpg?v=334ca088dc|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/EA888_2.jpg?v=dfb4c007bb|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/EA888_3.jpg?v=a0f5f5592e</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>filtr-dsg7-dq200</t>
+          <t>WHT001922</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-dsg7-dq200_1.jpg?v=817beb8c10</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/WHT001922_1.jpg?v=bb075186cb</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>filtr-setka-0b5-orig</t>
+          <t>filtr-dsg7-dq200</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_1.jpg?v=be20ada597|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_2.jpg?v=87268821a3</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-dsg7-dq200_1.jpg?v=817beb8c10|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-dsg7-dq200_2.png?v=b1ce9f5f30</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>gidroakkumulyator-orig</t>
+          <t>filtr-dsg7-dq500</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_1.jpg?v=51769ba372|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_2.jpg?v=2344c05b66|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_3.jpg?v=39719028b1</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-dsg7-dq500_1.png?v=5a2f360fb5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>jf011e</t>
+          <t>filtr-setka-0b5-orig</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/jf011e_1.jpg?v=e8e0f28d81|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/jf011e_2.jpg?v=fd3d1e7343</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_1.jpg?v=96f21d0cb5|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_2.jpg?v=be20ada597|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_3.jpg?v=87268821a3</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>klipsy-shtokov-2sht</t>
+          <t>gidroakkumulyator-orig</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/klipsy-shtokov-2sht_2.jpg?v=5cb33fddae</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_1.jpg?v=51769ba372|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_2.jpg?v=2344c05b66|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_3.jpg?v=39719028b1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>nakladki-pedali</t>
+          <t>jf011e</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/nakladki-pedali_1.jpg?v=c459949afe|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/nakladki-pedali_2.jpg?v=20a8430969</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/jf011e_1.jpg?v=e8e0f28d81|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/jf011e_2.jpg?v=fd3d1e7343</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>planka-solenoid-2sht</t>
+          <t>klipsy-shtokov-2sht</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/planka-solenoid-2sht_1.jpg?v=9d40871c3a</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/klipsy-shtokov-2sht_2.jpg?v=5cb33fddae</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>plastiny-solenoid-orig</t>
+          <t>kryshka-mehatronika-dq200</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastiny-solenoid-orig_1.jpg?v=d1b347b9af|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastiny-solenoid-orig_2.jpg?v=abefbc6b13</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/kryshka-mehatronika-dq200_1.png?v=637a263fe5</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>plita-filtr</t>
+          <t>nakladki-pedali</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_1.jpg?v=efa8557d9d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_2.jpg?v=759d463fe2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_3.jpg?v=3f11b4e476</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/nakladki-pedali_1.jpg?v=c459949afe|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/nakladki-pedali_2.jpg?v=20a8430969</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>plita-filtr-orig</t>
+          <t>planka-solenoid-2sht</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-orig_1.jpg?v=33c4d4baf2</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/planka-solenoid-2sht_1.jpg?v=9d40871c3a</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki</t>
+          <t>plastina-solenoid-dq200</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_1.jpg?v=de55e47d7c|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_2.jpg?v=f0ac7e97a2</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastina-solenoid-dq200_1.png?v=e86dd4da7d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal-orig</t>
+          <t>plastiny-solenoid-orig</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-sal-orig_1.jpg?v=663e730ff0</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastiny-solenoid-orig_1.jpg?v=d1b347b9af|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastiny-solenoid-orig_2.jpg?v=abefbc6b13</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki</t>
+          <t>plita-filtr</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki_1.jpg?v=03ce24da06</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_1.jpg?v=7c348500b1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_2.jpg?v=efa8557d9d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_3.jpg?v=759d463fe2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_4.jpg?v=3f11b4e476</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>podshipnik-vilki-6</t>
+          <t>plita-filtr-orig</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_1.jpg?v=1755bb55b2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_2.jpg?v=db91a4455e</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-orig_1.jpg?v=33c4d4baf2</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
+          <t>plita-filtr-pylniki</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki-v2_1.jpg?v=822e115d3a|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki-v2_2.jpg?v=67c916a623</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_1.jpg?v=de55e47d7c|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_2.jpg?v=f0ac7e97a2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig-v2</t>
+          <t>plita-filtr-pylniki-orig</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/remkomplekt-shtokov-orig-v2_1.jpg?v=f8bf2b9112</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-orig_1.jpg?v=ea76b2dfed|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-orig_2.jpg?v=13840cc30d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig</t>
+          <t>plita-filtr-pylniki-sal-orig</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_1.jpg?v=e5a1740eeb|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_2.jpg?v=b6e630000c</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-sal-orig_1.jpg?v=663e730ff0</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>salnik-tolkatelya-alum</t>
+          <t>plita-filtr-salniki-orig</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-tolkatelya-alum_1.jpg?v=b8838939fa</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig_1.jpg?v=38f0e2c7db|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig_2.jpg?v=2107be3341</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>salniki-shtokov-2sht</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-2sht_1.jpg?v=aa8f5c5cf2</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-v2_1.jpg?v=17dc040af2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-v2_2.jpg?v=aba4a8da4b</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>salniki-shtokov-orig</t>
+          <t>plita-pylniki-salniki</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-orig_1.jpg?v=4c8e4d8db5</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki_1.jpg?v=fe0eb62b49|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki_2.jpg?v=03ce24da06</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>salniki-tolkatelya-4sht</t>
+          <t>plita-pylniki-salniki-orig</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_1.jpg?v=28323f6201|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_2.jpg?v=37b0cc95a1</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig_1.jpg?v=d138fd63ef|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig_2.jpg?v=ca60bf2a09</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>salnikprivod-l</t>
+          <t>plita-pylniki-salniki-orig-v2</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-l_1.jpg?v=2394757996</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig-v2_1.jpg?v=851807b7d1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig-v2_2.jpg?v=ca60bf2a09</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>salnikprivod-r</t>
+          <t>podshipnik-vilki-6</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-r_1.jpg?v=c7ca0aca75</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_1.jpg?v=2476776fae|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_2.jpg?v=1755bb55b2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_3.jpg?v=db91a4455e</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>salnikvhod</t>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_1.jpg?v=fa7536c413|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_2.jpg?v=dc80d0c822</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki-v2_1.jpg?v=822e115d3a|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki-v2_2.jpg?v=67c916a623</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>stalnaya-vstavka-plity</t>
+          <t>prokladka-kryshki-dq200</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/stalnaya-vstavka-plity_1.jpg?v=b5aa54fe7d</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-kryshki-dq200_1.png?v=be7cbb92a8</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>tolkateli-4-salniki-4</t>
+          <t>prokladka-vtulki-dq200</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-4-salniki-4_1.jpg?v=6dd3ccd233</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-dq200_1.png?v=82b8b6682c</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>tolkateli-salniki-alum-komplekt</t>
+          <t>remkomplekt-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-salniki-alum-komplekt_1.jpg?v=c2f7c0583b</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/remkomplekt-shtokov-orig-v2_1.jpg?v=f8bf2b9112</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>salnik-shtoka-orig</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_1.jpg?v=e5a1740eeb|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_2.jpg?v=b6e630000c</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>salnik-tolkatelya-alum</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-tolkatelya-alum_1.jpg?v=b8838939fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>salniki-shtokov-2sht</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-2sht_1.jpg?v=08b49883ce|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-2sht_2.jpg?v=aa8f5c5cf2</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>salniki-shtokov-orig</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-orig_1.jpg?v=4c8e4d8db5</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>salniki-tolkatelya-4sht</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_1.jpg?v=28323f6201|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_2.jpg?v=37b0cc95a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>salnikprivod-l</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-l_1.jpg?v=2394757996</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>salnikprivod-r</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-r_1.jpg?v=c7ca0aca75</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>salnikvhod</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_1.jpg?v=fa7536c413|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_2.jpg?v=dc80d0c822</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>separatornaya-plastina-dq200</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/separatornaya-plastina-dq200_1.png?v=7ff85d1a3c</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>stalnaya-vstavka-plity</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/stalnaya-vstavka-plity_1.jpg?v=b5aa54fe7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>tolkateli-4-salniki-4</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-4-salniki-4_1.jpg?v=6dd3ccd233</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>tolkateli-salniki-alum-komplekt</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-salniki-alum-komplekt_1.jpg?v=c2f7c0583b</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
           <t>vtulki-shtokov-2sht</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/vtulki-shtokov-2sht_1.jpg?v=c43f734ce2</t>
         </is>

--- a/data/avito_photos.xlsx
+++ b/data/avito_photos.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025._1.jpg?v=32a4eaa349|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025._2.jpg?v=3f30a503c8</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025-cyr-s_1.jpg?v=32a4eaa349|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025-cyr-s_2.jpg?v=3f30a503c8</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._1.jpg?v=3e0abf9ec7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._2.jpg?v=b12c6dac21|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0._3.jpg?v=bd237a81d2</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0-cyr-sc_1.jpg?v=3e0abf9ec7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0-cyr-sc_2.jpg?v=b12c6dac21|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0-cyr-sc_3.jpg?v=bd237a81d2</t>
         </is>
       </c>
     </row>

--- a/data/avito_photos.xlsx
+++ b/data/avito_photos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B85"/>
+  <dimension ref="A1:B86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -887,550 +887,562 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>317053TX0C</t>
+          <t>123014‑AF</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_1.jpg?v=ff760a00af|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_2.jpg?v=8cf63c6906</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_1.jpg?v=7eebff5ddc|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_2.png?v=e9725022b3</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>55565480</t>
+          <t>317053TX0C</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/55565480_1.jpg?v=0ff6bde457</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_1.jpg?v=ff760a00af|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_2.jpg?v=8cf63c6906</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>6t30</t>
+          <t>55565480</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/6t30_1.jpg?v=eb7c8272e8</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/55565480_1.jpg?v=0ff6bde457</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Dq200dsg70am0cw</t>
+          <t>6t30</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq200dsg70am0cw_1.jpg?v=0087449119</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/6t30_1.jpg?v=eb7c8272e8</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Dq500</t>
+          <t>Dq200dsg70am0cw</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_1.jpg?v=b2dce2c6a2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_10.jpg?v=4782f6a203|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_11.jpg?v=b00b729a6f|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_12.jpg?v=3e5bb95f61|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_13.jpg?v=b5e4690bb8|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_14.jpg?v=293affdbb4|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_2.jpg?v=01450abeda|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_3.jpg?v=8b53715593|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_4.jpg?v=87672fa5cf|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_5.jpg?v=22b635f676|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_6.jpg?v=60c3947305|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_7.jpg?v=6455c2a999|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_8.jpg?v=1c56d278b5|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_9.jpg?v=0e28b9ca1b</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq200dsg70am0cw_1.jpg?v=0087449119</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>EA888</t>
+          <t>Dq500</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/EA888_1.jpg?v=334ca088dc|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/EA888_2.jpg?v=dfb4c007bb|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/EA888_3.jpg?v=a0f5f5592e</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_1.jpg?v=b2dce2c6a2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_2.jpg?v=01450abeda|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_3.jpg?v=8b53715593|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_4.jpg?v=87672fa5cf|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_5.jpg?v=22b635f676|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_6.jpg?v=60c3947305|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_7.jpg?v=6455c2a999|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_8.jpg?v=1c56d278b5|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_9.jpg?v=0e28b9ca1b|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_10.jpg?v=4782f6a203</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>WHT001922</t>
+          <t>EA888</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/WHT001922_1.jpg?v=bb075186cb</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/EA888_1.jpg?v=334ca088dc|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/EA888_2.jpg?v=dfb4c007bb|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/EA888_3.jpg?v=a0f5f5592e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>filtr-dsg7-dq200</t>
+          <t>WHT001922</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-dsg7-dq200_1.jpg?v=817beb8c10|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-dsg7-dq200_2.png?v=b1ce9f5f30</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/WHT001922_1.jpg?v=bb075186cb</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>filtr-dsg7-dq500</t>
+          <t>filtr-dsg7-dq200</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-dsg7-dq500_1.png?v=5a2f360fb5</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-dsg7-dq200_1.jpg?v=817beb8c10|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-dsg7-dq200_2.png?v=b1ce9f5f30</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>filtr-setka-0b5-orig</t>
+          <t>filtr-dsg7-dq500</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_1.jpg?v=96f21d0cb5|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_2.jpg?v=be20ada597|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_3.jpg?v=87268821a3</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-dsg7-dq500_1.png?v=5a2f360fb5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>gidroakkumulyator-orig</t>
+          <t>filtr-setka-0b5-orig</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_1.jpg?v=51769ba372|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_2.jpg?v=2344c05b66|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_3.jpg?v=39719028b1</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_1.jpg?v=96f21d0cb5|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_2.jpg?v=be20ada597|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_3.jpg?v=87268821a3</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>jf011e</t>
+          <t>gidroakkumulyator-orig</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/jf011e_1.jpg?v=e8e0f28d81|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/jf011e_2.jpg?v=fd3d1e7343</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_1.jpg?v=51769ba372|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_2.jpg?v=2344c05b66|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_3.jpg?v=39719028b1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>klipsy-shtokov-2sht</t>
+          <t>jf011e</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/klipsy-shtokov-2sht_2.jpg?v=5cb33fddae</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/jf011e_1.jpg?v=e8e0f28d81|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/jf011e_2.jpg?v=fd3d1e7343</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>kryshka-mehatronika-dq200</t>
+          <t>klipsy-shtokov-2sht</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/kryshka-mehatronika-dq200_1.png?v=637a263fe5</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/klipsy-shtokov-2sht_2.jpg?v=5cb33fddae</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>nakladki-pedali</t>
+          <t>kryshka-mehatronika-dq200</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/nakladki-pedali_1.jpg?v=c459949afe|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/nakladki-pedali_2.jpg?v=20a8430969</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/kryshka-mehatronika-dq200_1.jpg?v=8e1deb51de|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/kryshka-mehatronika-dq200_2.png?v=637a263fe5</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>planka-solenoid-2sht</t>
+          <t>nakladki-pedali</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/planka-solenoid-2sht_1.jpg?v=9d40871c3a</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/nakladki-pedali_1.jpg?v=c459949afe|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/nakladki-pedali_2.jpg?v=20a8430969</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>plastina-solenoid-dq200</t>
+          <t>planka-solenoid-2sht</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastina-solenoid-dq200_1.png?v=e86dd4da7d</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/planka-solenoid-2sht_1.jpg?v=9d40871c3a</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>plastiny-solenoid-orig</t>
+          <t>plastina-solenoid-dq200</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastiny-solenoid-orig_1.jpg?v=d1b347b9af|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastiny-solenoid-orig_2.jpg?v=abefbc6b13</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastina-solenoid-dq200_1.png?v=e86dd4da7d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>plita-filtr</t>
+          <t>plastiny-solenoid-orig</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_1.jpg?v=7c348500b1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_2.jpg?v=efa8557d9d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_3.jpg?v=759d463fe2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_4.jpg?v=3f11b4e476</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastiny-solenoid-orig_1.jpg?v=d1b347b9af|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastiny-solenoid-orig_2.jpg?v=abefbc6b13</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>plita-filtr-orig</t>
+          <t>plita-filtr</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-orig_1.jpg?v=33c4d4baf2</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_1.jpg?v=7c348500b1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_2.jpg?v=efa8557d9d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_3.jpg?v=759d463fe2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_4.jpg?v=3f11b4e476</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki</t>
+          <t>plita-filtr-orig</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_1.jpg?v=de55e47d7c|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_2.jpg?v=f0ac7e97a2</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-orig_1.jpg?v=33c4d4baf2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-orig</t>
+          <t>plita-filtr-pylniki</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-orig_1.jpg?v=ea76b2dfed|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-orig_2.jpg?v=13840cc30d</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_1.jpg?v=6562ad9b05|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_2.jpg?v=de55e47d7c|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_3.jpg?v=f0ac7e97a2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal-orig</t>
+          <t>plita-filtr-pylniki-orig</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-sal-orig_1.jpg?v=663e730ff0</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-orig_1.jpg?v=ea76b2dfed|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-orig_2.jpg?v=13840cc30d</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>plita-filtr-salniki-orig</t>
+          <t>plita-filtr-pylniki-sal-orig</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig_1.jpg?v=38f0e2c7db|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig_2.jpg?v=2107be3341</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-sal-orig_1.jpg?v=d831bae612|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-sal-orig_2.jpg?v=663e730ff0</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>plita-filtr-salniki-orig</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-v2_1.jpg?v=17dc040af2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-v2_2.jpg?v=aba4a8da4b</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig_1.jpg?v=38f0e2c7db|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig_2.jpg?v=2107be3341</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki_1.jpg?v=fe0eb62b49|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki_2.jpg?v=03ce24da06</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-v2_1.jpg?v=17dc040af2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-v2_2.jpg?v=aba4a8da4b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig</t>
+          <t>plita-pylniki-salniki</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig_1.jpg?v=d138fd63ef|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig_2.jpg?v=ca60bf2a09</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki_1.jpg?v=fe0eb62b49|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki_2.jpg?v=03ce24da06</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig-v2</t>
+          <t>plita-pylniki-salniki-orig</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig-v2_1.jpg?v=851807b7d1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig-v2_2.jpg?v=ca60bf2a09</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig_1.jpg?v=d138fd63ef|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig_2.jpg?v=ca60bf2a09</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>podshipnik-vilki-6</t>
+          <t>plita-pylniki-salniki-orig-v2</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_1.jpg?v=2476776fae|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_2.jpg?v=1755bb55b2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_3.jpg?v=db91a4455e</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig-v2_1.jpg?v=851807b7d1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig-v2_2.jpg?v=ca60bf2a09</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
+          <t>podshipnik-vilki-6</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki-v2_1.jpg?v=822e115d3a|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki-v2_2.jpg?v=67c916a623</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_1.jpg?v=2476776fae|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_2.jpg?v=1755bb55b2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_3.jpg?v=db91a4455e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>prokladka-kryshki-dq200</t>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-kryshki-dq200_1.png?v=be7cbb92a8</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki-v2_1.jpg?v=822e115d3a|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki-v2_2.jpg?v=67c916a623</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-dq200</t>
+          <t>prokladka-kryshki-dq200</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-dq200_1.png?v=82b8b6682c</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-kryshki-dq200_1.png?v=be7cbb92a8</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig-v2</t>
+          <t>prokladka-vtulki-dq200</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/remkomplekt-shtokov-orig-v2_1.jpg?v=f8bf2b9112</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-dq200_1.png?v=82b8b6682c</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig</t>
+          <t>remkomplekt-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_1.jpg?v=e5a1740eeb|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_2.jpg?v=b6e630000c</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/remkomplekt-shtokov-orig-v2_1.jpg?v=f8bf2b9112</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>salnik-tolkatelya-alum</t>
+          <t>salnik-shtoka-orig</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-tolkatelya-alum_1.jpg?v=b8838939fa</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_1.jpg?v=e5a1740eeb|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_2.jpg?v=b6e630000c</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>salniki-shtokov-2sht</t>
+          <t>salnik-tolkatelya-alum</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-2sht_1.jpg?v=08b49883ce|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-2sht_2.jpg?v=aa8f5c5cf2</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-tolkatelya-alum_1.jpg?v=b8838939fa</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>salniki-shtokov-orig</t>
+          <t>salniki-shtokov-2sht</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-orig_1.jpg?v=4c8e4d8db5</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-2sht_1.jpg?v=08b49883ce|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-2sht_2.jpg?v=aa8f5c5cf2</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>salniki-tolkatelya-4sht</t>
+          <t>salniki-shtokov-orig</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_1.jpg?v=28323f6201|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_2.jpg?v=37b0cc95a1</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-orig_1.jpg?v=4c8e4d8db5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>salnikprivod-l</t>
+          <t>salniki-tolkatelya-4sht</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-l_1.jpg?v=2394757996</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_1.jpg?v=28323f6201|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_2.jpg?v=37b0cc95a1</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>salnikprivod-r</t>
+          <t>salnikprivod-l</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-r_1.jpg?v=c7ca0aca75</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-l_1.jpg?v=2394757996</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>salnikvhod</t>
+          <t>salnikprivod-r</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_1.jpg?v=fa7536c413|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_2.jpg?v=dc80d0c822</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-r_1.jpg?v=c7ca0aca75</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>separatornaya-plastina-dq200</t>
+          <t>salnikvhod</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/separatornaya-plastina-dq200_1.png?v=7ff85d1a3c</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_1.jpg?v=fa7536c413|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_2.jpg?v=dc80d0c822</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>stalnaya-vstavka-plity</t>
+          <t>separatornaya-plastina-dq200</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/stalnaya-vstavka-plity_1.jpg?v=b5aa54fe7d</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/separatornaya-plastina-dq200_1.png?v=7ff85d1a3c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>tolkateli-4-salniki-4</t>
+          <t>stalnaya-vstavka-plity</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-4-salniki-4_1.jpg?v=6dd3ccd233</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/stalnaya-vstavka-plity_1.jpg?v=b5aa54fe7d</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>tolkateli-salniki-alum-komplekt</t>
+          <t>tolkateli-4-salniki-4</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-salniki-alum-komplekt_1.jpg?v=c2f7c0583b</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-4-salniki-4_1.jpg?v=6dd3ccd233</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>tolkateli-salniki-alum-komplekt</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-salniki-alum-komplekt_1.jpg?v=c2f7c0583b</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
           <t>vtulki-shtokov-2sht</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/vtulki-shtokov-2sht_1.jpg?v=c43f734ce2</t>
         </is>

--- a/data/avito_photos.xlsx
+++ b/data/avito_photos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B86"/>
+  <dimension ref="A1:B87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,958 +491,970 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0AM325219C</t>
+          <t>0AM325120A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325219C_1.jpg?v=e5d075d0e9</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325120A_1.jpg?v=53131c62ab</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0AM325413A</t>
+          <t>0AM325219C</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_1.jpg?v=3e45838a06</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325219C_1.jpg?v=e5d075d0e9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0AM325433E</t>
+          <t>0AM325413A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325433E_1.jpg?v=3a3aaf7762</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325413A_1.jpg?v=3e45838a06</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0AM325443D</t>
+          <t>0AM325433E</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_1.jpg?v=c45a2498aa|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_2.jpg?v=44a9ab31fd</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325433E_1.jpg?v=3a3aaf7762</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0AM325467J</t>
+          <t>0AM325443D</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325467J_1.jpg?v=70f40f556e</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_1.jpg?v=c45a2498aa|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325443D_2.jpg?v=44a9ab31fd</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0AM325473</t>
+          <t>0AM325467J</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=9d51d969ea</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325467J_1.jpg?v=70f40f556e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0AM325587E</t>
+          <t>0AM325473</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_1.jpg?v=6cc2257c48</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325473_1.jpg?v=9d51d969ea</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0AM927769D</t>
+          <t>0AM325587E</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769D_2.jpg?v=4529f855b6</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM325587E_1.jpg?v=6cc2257c48</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0AM927769N</t>
+          <t>0AM927769D</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769N_1.jpg?v=fbdb72784c</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769D_2.jpg?v=4529f855b6</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0am325025D</t>
+          <t>0AM927769N</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025D_1.jpg?v=bf2cf0a479</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM927769N_1.jpg?v=fbdb72784c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0am325025G</t>
+          <t>0am325025D</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_1.jpg?v=5bd8ad5ac3|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_2.jpg?v=21cf6a4fc0</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025D_1.jpg?v=bf2cf0a479</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0am325025H</t>
+          <t>0am325025G</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H_1.png?v=0593c687c2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H_2.jpg?v=df6ff84458</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_1.jpg?v=5bd8ad5ac3|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025G_2.jpg?v=21cf6a4fc0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0am325025HX</t>
+          <t>0am325025H</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_1.jpg?v=815184defd</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H_1.png?v=0593c687c2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025H_2.jpg?v=df6ff84458</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0am325025ae</t>
+          <t>0am325025HX</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025ae_1.jpg?v=e1a894f60b</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025HX_1.jpg?v=815184defd</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0am325025hfe</t>
+          <t>0am325025ae</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025hfe_1.jpg?v=23a46f0590</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025ae_1.jpg?v=e1a894f60b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0am325025j</t>
+          <t>0am325025hfe</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_1.jpg?v=5f0a06c746|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_2.jpg?v=f610170a4d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_3.jpg?v=77f42b52d2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_4.jpg?v=714b21e00d</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025hfe_1.jpg?v=23a46f0590</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0am325025l</t>
+          <t>0am325025j</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025l_1.jpg?v=c010c7bbdf</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_1.jpg?v=5f0a06c746|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_2.jpg?v=f610170a4d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_3.jpg?v=77f42b52d2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025j_4.jpg?v=714b21e00d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0am325025m</t>
+          <t>0am325025l</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025m_1.jpg?v=ba44318fd7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025m_2.jpg?v=fd9283f1f7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025m_3.jpg?v=b7ac56b9b3</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025l_1.jpg?v=c010c7bbdf</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0am325025q</t>
+          <t>0am325025m</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025q_1.jpg?v=5190638fc3|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025q_2.jpg?v=77fc244bbc|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025q_3.jpg?v=4d3606b157</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025m_1.jpg?v=ba44318fd7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025m_2.jpg?v=fd9283f1f7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025m_3.jpg?v=b7ac56b9b3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0am325025r</t>
+          <t>0am325025q</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025r_1.jpg?v=3b3b076322</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025q_1.jpg?v=5190638fc3|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025q_2.jpg?v=77fc244bbc|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025q_3.jpg?v=4d3606b157</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0am325025С</t>
+          <t>0am325025r</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025-cyr-s_1.jpg?v=32a4eaa349|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025-cyr-s_2.jpg?v=3f30a503c8</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025r_1.jpg?v=3b3b076322</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0am325066AC</t>
+          <t>0am325025С</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066AC_1.jpg?v=693a4298e8</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025-cyr-s_1.jpg?v=32a4eaa349|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325025-cyr-s_2.jpg?v=3f30a503c8</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0am325066ad</t>
+          <t>0am325066AC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=cbeca4b59a|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_2.jpg?v=a9a9967b4d</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066AC_1.jpg?v=693a4298e8</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0am325066ae</t>
+          <t>0am325066ad</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_1.jpg?v=ffb6e141cb|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_2.jpg?v=1af750811c</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_1.jpg?v=cbeca4b59a|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ad_2.jpg?v=a9a9967b4d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0am325091e</t>
+          <t>0am325066ae</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e_1.jpg?v=ad51750acf|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e_2.jpg?v=579c860e1a</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_1.jpg?v=ffb6e141cb|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325066ae_2.jpg?v=1af750811c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0am325091f</t>
+          <t>0am325091e</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f_1.jpg?v=fc28fbc227|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f_2.jpg?v=94ce98509a</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e_1.jpg?v=ad51750acf|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091e_2.jpg?v=579c860e1a</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0am325477</t>
+          <t>0am325091f</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477_1.jpg?v=76f197e896</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f_1.jpg?v=fc28fbc227|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325091f_2.jpg?v=94ce98509a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0ambset</t>
+          <t>0am325477</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0ambset_1.jpg?v=ac2cbcb893|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0ambset_2.jpg?v=4021b295b7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0ambset_3.jpg?v=2c5f358ea8</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0am325477_1.jpg?v=76f197e896</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0cw0am</t>
+          <t>0ambset</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_1.jpg?v=d9a6257d65|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_2.jpg?v=2e5ae40f99|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_3.jpg?v=452fb81089</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0ambset_1.jpg?v=ac2cbcb893|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0ambset_2.jpg?v=4021b295b7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0ambset_3.jpg?v=2c5f358ea8</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0cw0am325025</t>
+          <t>0cw0am</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025_1.jpg?v=98f28523c2</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_1.jpg?v=d9a6257d65|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_2.jpg?v=2e5ae40f99|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am_3.jpg?v=452fb81089</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0cw0amdsgdq200</t>
+          <t>0cw0am325025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0amdsgdq200_1.jpg?v=d2723138aa|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0amdsgdq200_2.jpg?v=77a111eb34|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0amdsgdq200_3.jpg?v=40c2597cb3</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0am325025_1.jpg?v=98f28523c2</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0cw325025h</t>
+          <t>0cw0amdsgdq200</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_1.jpg?v=0c3047157b|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_2.jpg?v=209a640347</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0amdsgdq200_1.jpg?v=d2723138aa|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0amdsgdq200_2.jpg?v=77a111eb34|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw0amdsgdq200_3.jpg?v=40c2597cb3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0сц</t>
+          <t>0cw325025h</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0-cyr-sc_1.jpg?v=3e0abf9ec7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0-cyr-sc_2.jpg?v=b12c6dac21|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0-cyr-sc_3.jpg?v=bd237a81d2</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_1.jpg?v=0c3047157b|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0cw325025h_2.jpg?v=209a640347</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>123014‑AF</t>
+          <t>0сц</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_1.jpg?v=7eebff5ddc|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_2.png?v=e9725022b3</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0-cyr-sc_1.jpg?v=3e0abf9ec7|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0-cyr-sc_2.jpg?v=b12c6dac21|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0-cyr-sc_3.jpg?v=bd237a81d2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>317053TX0C</t>
+          <t>123014‑AF</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_1.jpg?v=ff760a00af|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_2.jpg?v=8cf63c6906</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_1.jpg?v=7eebff5ddc|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/123014.AF_2.png?v=e9725022b3</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>55565480</t>
+          <t>317053TX0C</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/55565480_1.jpg?v=0ff6bde457</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_1.jpg?v=ff760a00af|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/317053TX0C_2.jpg?v=8cf63c6906</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>6t30</t>
+          <t>55565480</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/6t30_1.jpg?v=eb7c8272e8</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/55565480_1.jpg?v=0ff6bde457</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Dq200dsg70am0cw</t>
+          <t>6t30</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq200dsg70am0cw_1.jpg?v=0087449119</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/6t30_1.jpg?v=eb7c8272e8</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Dq500</t>
+          <t>Dq200dsg70am0cw</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_1.jpg?v=b2dce2c6a2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_2.jpg?v=01450abeda|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_3.jpg?v=8b53715593|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_4.jpg?v=87672fa5cf|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_5.jpg?v=22b635f676|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_6.jpg?v=60c3947305|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_7.jpg?v=6455c2a999|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_8.jpg?v=1c56d278b5|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_9.jpg?v=0e28b9ca1b|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_10.jpg?v=4782f6a203</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq200dsg70am0cw_1.jpg?v=0087449119</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>EA888</t>
+          <t>Dq500</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/EA888_1.jpg?v=334ca088dc|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/EA888_2.jpg?v=dfb4c007bb|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/EA888_3.jpg?v=a0f5f5592e</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_1.jpg?v=b2dce2c6a2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_2.jpg?v=01450abeda|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_3.jpg?v=8b53715593|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_4.jpg?v=87672fa5cf|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_5.jpg?v=22b635f676|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_6.jpg?v=60c3947305|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_7.jpg?v=6455c2a999|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_8.jpg?v=1c56d278b5|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_9.jpg?v=0e28b9ca1b|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/Dq500_10.jpg?v=4782f6a203</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>WHT001922</t>
+          <t>EA888</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/WHT001922_1.jpg?v=bb075186cb</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/EA888_1.jpg?v=334ca088dc|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/EA888_2.jpg?v=dfb4c007bb|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/EA888_3.jpg?v=a0f5f5592e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>filtr-dsg7-dq200</t>
+          <t>WHT001922</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-dsg7-dq200_1.jpg?v=817beb8c10|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-dsg7-dq200_2.png?v=b1ce9f5f30</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/WHT001922_1.jpg?v=bb075186cb</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>filtr-dsg7-dq500</t>
+          <t>filtr-dsg7-dq200</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-dsg7-dq500_1.png?v=5a2f360fb5</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-dsg7-dq200_1.jpg?v=817beb8c10|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-dsg7-dq200_2.png?v=b1ce9f5f30</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>filtr-setka-0b5-orig</t>
+          <t>filtr-dsg7-dq500</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_1.jpg?v=96f21d0cb5|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_2.jpg?v=be20ada597|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_3.jpg?v=87268821a3</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-dsg7-dq500_1.png?v=5a2f360fb5</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>gidroakkumulyator-orig</t>
+          <t>filtr-setka-0b5-orig</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_1.jpg?v=51769ba372|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_2.jpg?v=2344c05b66|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_3.jpg?v=39719028b1</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_1.jpg?v=96f21d0cb5|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_2.jpg?v=be20ada597|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/filtr-setka-0b5-orig_3.jpg?v=87268821a3</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>jf011e</t>
+          <t>gidroakkumulyator-orig</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/jf011e_1.jpg?v=e8e0f28d81|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/jf011e_2.jpg?v=fd3d1e7343</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_1.jpg?v=51769ba372|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_2.jpg?v=2344c05b66|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/gidroakkumulyator-orig_3.jpg?v=39719028b1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>klipsy-shtokov-2sht</t>
+          <t>jf011e</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/klipsy-shtokov-2sht_2.jpg?v=5cb33fddae</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/jf011e_1.jpg?v=e8e0f28d81|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/jf011e_2.jpg?v=fd3d1e7343</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>kryshka-mehatronika-dq200</t>
+          <t>klipsy-shtokov-2sht</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/kryshka-mehatronika-dq200_1.jpg?v=8e1deb51de|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/kryshka-mehatronika-dq200_2.png?v=637a263fe5</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/klipsy-shtokov-2sht_2.jpg?v=5cb33fddae</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>nakladki-pedali</t>
+          <t>kryshka-mehatronika-dq200</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/nakladki-pedali_1.jpg?v=c459949afe|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/nakladki-pedali_2.jpg?v=20a8430969</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/kryshka-mehatronika-dq200_1.jpg?v=8e1deb51de|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/kryshka-mehatronika-dq200_2.png?v=637a263fe5</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>planka-solenoid-2sht</t>
+          <t>nakladki-pedali</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/planka-solenoid-2sht_1.jpg?v=9d40871c3a</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/nakladki-pedali_1.jpg?v=c459949afe|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/nakladki-pedali_2.jpg?v=20a8430969</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>plastina-solenoid-dq200</t>
+          <t>planka-solenoid-2sht</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastina-solenoid-dq200_1.png?v=e86dd4da7d</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/planka-solenoid-2sht_1.jpg?v=9d40871c3a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>plastiny-solenoid-orig</t>
+          <t>plastina-solenoid-dq200</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastiny-solenoid-orig_1.jpg?v=d1b347b9af|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastiny-solenoid-orig_2.jpg?v=abefbc6b13</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastina-solenoid-dq200_1.png?v=e86dd4da7d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>plita-filtr</t>
+          <t>plastiny-solenoid-orig</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_1.jpg?v=7c348500b1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_2.jpg?v=efa8557d9d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_3.jpg?v=759d463fe2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_4.jpg?v=3f11b4e476</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastiny-solenoid-orig_1.jpg?v=d1b347b9af|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plastiny-solenoid-orig_2.jpg?v=abefbc6b13</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>plita-filtr-orig</t>
+          <t>plita-filtr</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-orig_1.jpg?v=33c4d4baf2</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_1.jpg?v=7c348500b1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_2.jpg?v=efa8557d9d|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_3.jpg?v=759d463fe2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr_4.jpg?v=3f11b4e476</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki</t>
+          <t>plita-filtr-orig</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_1.jpg?v=6562ad9b05|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_2.jpg?v=de55e47d7c|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_3.jpg?v=f0ac7e97a2</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-orig_1.jpg?v=33c4d4baf2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-orig</t>
+          <t>plita-filtr-pylniki</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-orig_1.jpg?v=ea76b2dfed|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-orig_2.jpg?v=13840cc30d</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_1.jpg?v=6562ad9b05|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_2.jpg?v=de55e47d7c|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki_3.jpg?v=f0ac7e97a2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>plita-filtr-pylniki-sal-orig</t>
+          <t>plita-filtr-pylniki-orig</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-sal-orig_1.jpg?v=d831bae612|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-sal-orig_2.jpg?v=663e730ff0</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-orig_1.jpg?v=ea76b2dfed|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-orig_2.jpg?v=13840cc30d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>plita-filtr-salniki-orig</t>
+          <t>plita-filtr-pylniki-sal-orig</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig_1.jpg?v=38f0e2c7db|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig_2.jpg?v=2107be3341</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-sal-orig_1.jpg?v=d831bae612|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-pylniki-sal-orig_2.jpg?v=663e730ff0</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>plita-filtr-v2</t>
+          <t>plita-filtr-salniki-orig</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-v2_1.jpg?v=17dc040af2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-v2_2.jpg?v=aba4a8da4b</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig_1.jpg?v=38f0e2c7db|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-salniki-orig_2.jpg?v=2107be3341</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki</t>
+          <t>plita-filtr-v2</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki_1.jpg?v=fe0eb62b49|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki_2.jpg?v=03ce24da06</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-v2_1.jpg?v=17dc040af2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-filtr-v2_2.jpg?v=aba4a8da4b</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig</t>
+          <t>plita-pylniki-salniki</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig_1.jpg?v=d138fd63ef|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig_2.jpg?v=ca60bf2a09</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki_1.jpg?v=fe0eb62b49|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki_2.jpg?v=03ce24da06</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>plita-pylniki-salniki-orig-v2</t>
+          <t>plita-pylniki-salniki-orig</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig-v2_1.jpg?v=851807b7d1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig-v2_2.jpg?v=ca60bf2a09</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig_1.jpg?v=d138fd63ef|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig_2.jpg?v=ca60bf2a09</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>podshipnik-vilki-6</t>
+          <t>plita-pylniki-salniki-orig-v2</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_1.jpg?v=2476776fae|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_2.jpg?v=1755bb55b2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_3.jpg?v=db91a4455e</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig-v2_1.jpg?v=851807b7d1|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/plita-pylniki-salniki-orig-v2_2.jpg?v=ca60bf2a09</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>porshni-usil-pylniki-kryshki-v2</t>
+          <t>podshipnik-vilki-6</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki-v2_1.jpg?v=822e115d3a|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki-v2_2.jpg?v=67c916a623</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_1.jpg?v=2476776fae|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_2.jpg?v=1755bb55b2|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/podshipnik-vilki-6_3.jpg?v=db91a4455e</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>prokladka-kryshki-dq200</t>
+          <t>porshni-usil-pylniki-kryshki-v2</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-kryshki-dq200_1.png?v=be7cbb92a8</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki-v2_1.jpg?v=822e115d3a|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/porshni-usil-pylniki-kryshki-v2_2.jpg?v=67c916a623</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>prokladka-vtulki-dq200</t>
+          <t>prokladka-kryshki-dq200</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-dq200_1.png?v=82b8b6682c</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-kryshki-dq200_1.png?v=be7cbb92a8</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>remkomplekt-shtokov-orig-v2</t>
+          <t>prokladka-vtulki-dq200</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/remkomplekt-shtokov-orig-v2_1.jpg?v=f8bf2b9112</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-dq200_1.png?v=82b8b6682c</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>salnik-shtoka-orig</t>
+          <t>remkomplekt-shtokov-orig-v2</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_1.jpg?v=e5a1740eeb|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_2.jpg?v=b6e630000c</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/remkomplekt-shtokov-orig-v2_1.jpg?v=f8bf2b9112</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>salnik-tolkatelya-alum</t>
+          <t>salnik-shtoka-orig</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-tolkatelya-alum_1.jpg?v=b8838939fa</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_1.jpg?v=e5a1740eeb|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-shtoka-orig_2.jpg?v=b6e630000c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>salniki-shtokov-2sht</t>
+          <t>salnik-tolkatelya-alum</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-2sht_1.jpg?v=08b49883ce|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-2sht_2.jpg?v=aa8f5c5cf2</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnik-tolkatelya-alum_1.jpg?v=b8838939fa</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>salniki-shtokov-orig</t>
+          <t>salniki-shtokov-2sht</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-orig_1.jpg?v=4c8e4d8db5</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-2sht_1.jpg?v=08b49883ce|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-2sht_2.jpg?v=aa8f5c5cf2</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>salniki-tolkatelya-4sht</t>
+          <t>salniki-shtokov-orig</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_1.jpg?v=28323f6201|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_2.jpg?v=37b0cc95a1</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-shtokov-orig_1.jpg?v=4c8e4d8db5</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>salnikprivod-l</t>
+          <t>salniki-tolkatelya-4sht</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-l_1.jpg?v=2394757996</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_1.jpg?v=28323f6201|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salniki-tolkatelya-4sht_2.jpg?v=37b0cc95a1</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>salnikprivod-r</t>
+          <t>salnikprivod-l</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-r_1.jpg?v=c7ca0aca75</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-l_1.jpg?v=2394757996</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>salnikvhod</t>
+          <t>salnikprivod-r</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_1.jpg?v=fa7536c413|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_2.jpg?v=dc80d0c822</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikprivod-r_1.jpg?v=c7ca0aca75</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>separatornaya-plastina-dq200</t>
+          <t>salnikvhod</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/separatornaya-plastina-dq200_1.png?v=7ff85d1a3c</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_1.jpg?v=fa7536c413|https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/salnikvhod_2.jpg?v=dc80d0c822</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>stalnaya-vstavka-plity</t>
+          <t>separatornaya-plastina-dq200</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/stalnaya-vstavka-plity_1.jpg?v=b5aa54fe7d</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/separatornaya-plastina-dq200_1.png?v=7ff85d1a3c</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>tolkateli-4-salniki-4</t>
+          <t>stalnaya-vstavka-plity</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-4-salniki-4_1.jpg?v=6dd3ccd233</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/stalnaya-vstavka-plity_1.jpg?v=b5aa54fe7d</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>tolkateli-salniki-alum-komplekt</t>
+          <t>tolkateli-4-salniki-4</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-salniki-alum-komplekt_1.jpg?v=c2f7c0583b</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-4-salniki-4_1.jpg?v=6dd3ccd233</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
+          <t>tolkateli-salniki-alum-komplekt</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/tolkateli-salniki-alum-komplekt_1.jpg?v=c2f7c0583b</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
           <t>vtulki-shtokov-2sht</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/vtulki-shtokov-2sht_1.jpg?v=c43f734ce2</t>
         </is>

--- a/data/avito_photos.xlsx
+++ b/data/avito_photos.xlsx
@@ -1288,7 +1288,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-dq200_1.png?v=82b8b6682c</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-dq200_1.png?v=6e4db825ca</t>
         </is>
       </c>
     </row>

--- a/data/avito_photos.xlsx
+++ b/data/avito_photos.xlsx
@@ -1288,7 +1288,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-dq200_1.png?v=6e4db825ca</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-dq200_1.png?v=8312c47b41</t>
         </is>
       </c>
     </row>

--- a/data/avito_photos.xlsx
+++ b/data/avito_photos.xlsx
@@ -472,7 +472,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.jpg?v=65c46f9b97</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/0AM301212A_1.jpg?v=94573cf68b</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-dq200_1.png?v=8312c47b41</t>
+          <t>https://github.com/antongrigorenko844-prog/marketplace-agent/releases/download/product-photos/prokladka-vtulki-dq200_1.png?v=e3f97523c1</t>
         </is>
       </c>
     </row>
